--- a/software/python_processing/results/Binary Training Results.xlsx
+++ b/software/python_processing/results/Binary Training Results.xlsx
@@ -425,27 +425,4623 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A4"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LDA BAccuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LDA Accuracy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LDA F1 Score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LDA AUC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LDA AP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LDA Kappa</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LDA AUPRC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LDA EER</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LDA TPR@10%FPR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LDA TPR@5%FPR</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Experiment</t>
+          <t>cLACIr AvP Task -1.0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>54.88 ± 7.81</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>54.24 ± 7.05</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>55.24 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>55.23 ± 9.71</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>57.94 ± 20.80</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>57.93 ± 20.81</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>46.09 ± 7.62</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>20.01 ± 11.66</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>13.08 ± 10.57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>cLASIr AvP Task, No Accelerometer</t>
+          <t>cLACIr Int Task -1.0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>83.58 ± 5.68</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>82.88 ± 5.64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>83.06 ± 5.71</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>89.09 ± 6.77</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>89.87 ± 9.93</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.64 ± 0.11</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>89.86 ± 9.95</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>17.30 ± 6.54</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>76.50 ± 13.47</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>70.03 ± 16.31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>cLASIr Int Task, No Accelerometer</t>
+          <t>cLACIr AvP Task, No Accelerometer -1.0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>55.19 ± 7.29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53.00 ± 6.62</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>53.64 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>55.47 ± 8.79</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>55.67 ± 22.58</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>55.66 ± 22.58</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>45.19 ± 6.65</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16.35 ± 17.20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>12.26 ± 14.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -1.0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>67.24 ± 6.49</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>65.61 ± 5.04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>66.24 ± 5.13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>72.58 ± 6.96</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>72.57 ± 14.67</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.31 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>72.55 ± 14.69</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>32.92 ± 6.43</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>33.24 ± 14.38</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>23.01 ± 16.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.9</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>54.88 ± 7.81</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>54.24 ± 7.05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>55.24 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>55.23 ± 9.71</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>57.94 ± 20.80</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>57.93 ± 20.81</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>46.09 ± 7.62</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>20.01 ± 11.66</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>13.08 ± 10.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>83.58 ± 5.68</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>82.88 ± 5.64</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>83.06 ± 5.71</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>89.09 ± 6.77</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>89.87 ± 9.93</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.64 ± 0.11</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>89.86 ± 9.95</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>17.30 ± 6.54</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.50 ± 13.47</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>70.03 ± 16.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.9</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>55.19 ± 7.29</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>53.00 ± 6.62</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>53.64 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>55.47 ± 8.79</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>55.67 ± 22.58</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>55.66 ± 22.58</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>45.19 ± 6.65</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16.35 ± 17.20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>12.26 ± 14.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>67.24 ± 6.49</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>65.61 ± 5.04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>66.24 ± 5.13</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>72.58 ± 6.96</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>72.57 ± 14.67</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.31 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>72.55 ± 14.69</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>32.92 ± 6.43</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>33.24 ± 14.38</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>23.01 ± 16.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>54.88 ± 7.81</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>54.24 ± 7.05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>55.24 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>55.23 ± 9.71</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>57.94 ± 20.80</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>57.93 ± 20.81</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>46.09 ± 7.62</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>20.01 ± 11.66</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>13.08 ± 10.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>83.58 ± 5.68</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>82.88 ± 5.64</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>83.06 ± 5.71</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>89.09 ± 6.77</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>89.87 ± 9.93</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.64 ± 0.11</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>89.86 ± 9.95</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17.30 ± 6.54</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.50 ± 13.47</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>70.03 ± 16.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>55.19 ± 7.29</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>53.00 ± 6.62</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>53.64 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>55.47 ± 8.79</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>55.67 ± 22.58</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>55.66 ± 22.58</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>45.19 ± 6.65</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>16.35 ± 17.20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>12.26 ± 14.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>67.24 ± 6.49</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>65.61 ± 5.04</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>66.24 ± 5.13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>72.58 ± 6.96</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>72.57 ± 14.67</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.31 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>72.55 ± 14.69</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>32.92 ± 6.43</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>33.24 ± 14.38</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>23.01 ± 16.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>54.88 ± 7.81</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>54.24 ± 7.05</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>55.24 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>55.23 ± 9.71</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>57.94 ± 20.80</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>57.93 ± 20.81</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>46.09 ± 7.62</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>20.01 ± 11.66</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>13.08 ± 10.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.7</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>83.58 ± 5.68</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>82.88 ± 5.64</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>83.06 ± 5.71</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>89.09 ± 6.77</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>89.87 ± 9.93</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.64 ± 0.11</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>89.86 ± 9.95</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17.30 ± 6.54</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.50 ± 13.47</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>70.03 ± 16.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>55.19 ± 7.29</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>53.00 ± 6.62</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>53.64 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>55.47 ± 8.79</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>55.67 ± 22.58</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>55.66 ± 22.58</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>45.19 ± 6.65</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16.35 ± 17.20</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>12.26 ± 14.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.7</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>67.24 ± 6.49</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>65.61 ± 5.04</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>66.24 ± 5.13</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>72.58 ± 6.96</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>72.57 ± 14.67</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.31 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>72.55 ± 14.69</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>32.92 ± 6.43</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>33.24 ± 14.38</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>23.01 ± 16.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>54.88 ± 7.81</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>54.24 ± 7.05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>55.24 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>55.23 ± 9.71</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>57.94 ± 20.80</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>57.93 ± 20.81</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>46.09 ± 7.62</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>20.01 ± 11.66</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>13.08 ± 10.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>83.58 ± 5.68</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>82.88 ± 5.64</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>83.06 ± 5.71</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>89.09 ± 6.77</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>89.87 ± 9.93</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.64 ± 0.11</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>89.86 ± 9.95</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>17.30 ± 6.54</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.50 ± 13.47</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>70.03 ± 16.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>55.19 ± 7.29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>53.00 ± 6.62</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>53.64 ± 7.17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>55.47 ± 8.79</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>55.67 ± 22.58</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>55.66 ± 22.58</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>45.19 ± 6.65</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>16.35 ± 17.20</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>12.26 ± 14.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>67.24 ± 6.49</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>65.61 ± 5.04</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>66.24 ± 5.13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>72.58 ± 6.96</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>72.57 ± 14.67</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.31 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>72.55 ± 14.69</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>32.92 ± 6.43</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>33.24 ± 14.38</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>23.01 ± 16.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.5</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>54.62 ± 7.10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>54.14 ± 8.36</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>54.60 ± 8.67</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>55.94 ± 10.94</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>57.32 ± 15.38</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>57.30 ± 15.39</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>45.45 ± 8.66</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>19.05 ± 9.51</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>12.13 ± 7.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>83.59 ± 6.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>83.35 ± 6.45</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>83.33 ± 6.54</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>89.28 ± 6.88</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>90.98 ± 7.19</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.66 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>90.97 ± 7.20</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>16.67 ± 6.42</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.62 ± 12.07</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>69.79 ± 17.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>53.75 ± 6.51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>52.11 ± 8.13</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>52.60 ± 8.36</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>55.51 ± 8.88</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>55.62 ± 17.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.07 ± 0.13</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>55.61 ± 17.00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>45.73 ± 6.82</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>15.83 ± 10.00</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>9.17 ± 8.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>65.96 ± 13.07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>65.61 ± 13.07</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>65.58 ± 13.72</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>71.35 ± 15.35</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>72.40 ± 17.32</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.31 ± 0.26</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>72.39 ± 17.34</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>33.17 ± 12.58</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>39.22 ± 25.21</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>28.24 ± 23.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.4</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>53.88 ± 8.94</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>53.45 ± 7.05</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>53.32 ± 6.84</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>55.02 ± 12.96</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>55.86 ± 19.42</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.07 ± 0.16</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>55.85 ± 19.42</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>45.82 ± 9.99</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>19.03 ± 16.12</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13.13 ± 15.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>82.32 ± 6.97</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>82.86 ± 6.89</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>82.76 ± 6.99</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>87.47 ± 7.22</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>89.74 ± 7.20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.64 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>89.74 ± 7.20</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>18.18 ± 6.43</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>67.78 ± 25.67</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>62.03 ± 25.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>53.22 ± 8.85</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>51.76 ± 9.03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>51.61 ± 9.16</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>53.31 ± 12.41</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>55.17 ± 15.35</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.17</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>55.16 ± 15.35</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>46.78 ± 8.82</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>16.43 ± 11.62</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>8.18 ± 8.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>64.71 ± 5.83</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>65.25 ± 7.26</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>65.17 ± 7.16</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>69.80 ± 7.38</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.50 ± 10.48</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.29 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>69.48 ± 10.49</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35.81 ± 5.22</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>27.86 ± 15.87</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>16.89 ± 16.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>56.40 ± 5.23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>55.19 ± 5.66</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>56.14 ± 5.84</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>58.19 ± 7.39</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>56.09 ± 18.02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.11 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>56.08 ± 18.03</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>42.98 ± 5.84</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>17.51 ± 13.04</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>10.54 ± 9.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>81.99 ± 6.49</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>81.99 ± 6.73</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>82.19 ± 6.57</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>87.95 ± 5.75</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>88.14 ± 10.52</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.62 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>88.12 ± 10.54</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>18.70 ± 6.06</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>73.97 ± 11.92</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>69.38 ± 13.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>53.06 ± 4.47</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>51.46 ± 5.99</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>52.00 ± 6.95</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>53.64 ± 7.64</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>52.45 ± 15.90</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.08</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>52.44 ± 15.91</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>47.19 ± 5.69</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>14.08 ± 13.55</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>8.49 ± 11.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>65.50 ± 5.48</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>64.76 ± 5.04</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>64.88 ± 5.23</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>70.21 ± 6.76</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>68.89 ± 16.24</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.29 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>68.87 ± 16.26</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>35.02 ± 5.45</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>32.45 ± 12.98</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>19.51 ± 12.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>57.67 ± 7.03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>56.89 ± 6.63</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>57.36 ± 6.36</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>59.60 ± 8.68</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>56.67 ± 16.30</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>56.66 ± 16.30</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>42.30 ± 6.62</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>21.35 ± 15.04</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>14.68 ± 13.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>80.16 ± 10.37</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>81.27 ± 9.58</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>81.15 ± 9.66</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>85.27 ± 12.08</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>85.05 ± 14.98</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.60 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>85.03 ± 15.00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>21.47 ± 10.57</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>65.52 ± 23.90</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>61.07 ± 25.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>55.06 ± 6.77</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>54.27 ± 6.84</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>54.18 ± 6.29</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>55.45 ± 9.89</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>54.82 ± 14.89</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>54.81 ± 14.89</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>45.15 ± 6.09</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>18.63 ± 13.84</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>13.30 ± 12.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>65.23 ± 11.10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>65.66 ± 10.27</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>65.97 ± 10.15</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>69.97 ± 13.90</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>68.60 ± 16.86</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.29 ± 0.22</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>68.58 ± 16.87</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>34.56 ± 11.20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>28.29 ± 19.25</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>19.57 ± 18.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>55.65 ± 6.06</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>56.39 ± 7.51</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>55.80 ± 7.98</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>56.43 ± 9.16</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>51.11 ± 11.85</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.11 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>51.09 ± 11.85</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>44.48 ± 6.64</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>15.56 ± 11.15</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>8.98 ± 9.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>83.02 ± 9.12</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>84.36 ± 6.31</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>84.39 ± 6.31</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>88.34 ± 11.76</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>86.58 ± 15.94</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.65 ± 0.18</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>86.57 ± 15.96</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>19.05 ± 11.42</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>74.95 ± 17.12</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>68.62 ± 19.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>54.64 ± 6.41</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>56.60 ± 8.02</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>54.69 ± 8.71</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>53.17 ± 9.92</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>48.65 ± 11.25</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.10 ± 0.13</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>48.64 ± 11.25</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>47.56 ± 9.21</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>12.91 ± 8.70</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5.80 ± 5.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>66.45 ± 6.49</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>66.42 ± 7.16</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>66.92 ± 6.80</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>72.47 ± 7.54</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>67.71 ± 18.91</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.31 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>67.68 ± 18.94</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>33.28 ± 6.84</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>35.30 ± 14.24</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>23.41 ± 12.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task -0.0</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>57.67 ± 8.73</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>57.25 ± 7.36</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>57.23 ± 6.68</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>60.15 ± 12.27</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>55.80 ± 21.49</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.14 ± 0.16</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>55.79 ± 21.49</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>43.22 ± 10.16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>25.49 ± 16.92</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>18.75 ± 15.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task -0.0</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>84.09 ± 8.99</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>82.75 ± 9.48</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>82.82 ± 10.34</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>90.80 ± 8.72</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>88.22 ± 13.81</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.63 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>88.20 ± 13.86</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>16.04 ± 9.49</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>80.05 ± 16.56</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>73.64 ± 18.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer -0.0</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>55.38 ± 5.76</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>55.57 ± 6.88</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>54.06 ± 7.61</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>56.49 ± 8.07</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>51.47 ± 18.87</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.10 ± 0.11</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>51.46 ± 18.88</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>45.65 ± 6.67</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>18.91 ± 14.82</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14.02 ± 13.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer -0.0</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>67.00 ± 10.34</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>65.81 ± 9.88</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>66.29 ± 10.75</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>71.81 ± 12.48</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>66.24 ± 18.28</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.30 ± 0.19</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>66.21 ± 18.31</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>32.63 ± 10.03</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>36.67 ± 21.09</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>20.46 ± 16.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task 0.1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>54.38 ± 8.69</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>60.75 ± 8.71</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>58.79 ± 8.81</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>56.92 ± 14.62</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>47.24 ± 21.44</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.18</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>47.22 ± 21.45</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>44.83 ± 10.91</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>17.88 ± 16.21</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>12.39 ± 12.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task 0.1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>85.66 ± 9.53</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>85.46 ± 8.92</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>85.64 ± 8.93</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>91.90 ± 8.59</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>90.55 ± 10.63</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.68 ± 0.19</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>90.54 ± 10.64</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>13.97 ± 9.93</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>78.96 ± 19.36</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>72.45 ± 23.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer 0.1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>54.04 ± 9.72</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>61.58 ± 10.40</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>57.65 ± 11.28</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>54.38 ± 16.19</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>46.27 ± 22.50</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>46.25 ± 22.51</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>45.82 ± 12.00</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>19.98 ± 19.50</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>12.99 ± 14.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer 0.1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>68.13 ± 8.84</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>67.25 ± 7.38</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>67.14 ± 7.64</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>74.63 ± 12.74</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>65.04 ± 18.52</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.32 ± 0.15</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>64.99 ± 18.56</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30.52 ± 9.77</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>39.55 ± 21.03</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>25.74 ± 15.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task 0.2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>56.73 ± 7.70</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>63.59 ± 10.16</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>61.46 ± 11.18</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>60.92 ± 12.04</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>47.37 ± 16.02</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.14 ± 0.17</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>47.35 ± 16.03</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>42.49 ± 9.48</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>23.27 ± 15.39</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>15.68 ± 13.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task 0.2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>86.20 ± 5.13</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>86.68 ± 5.46</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>87.07 ± 5.81</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>80.67 ± 27.12</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>77.39 ± 26.66</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.62 ± 0.23</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>82.36 ± 12.73</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>14.20 ± 6.72</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>75.62 ± 14.99</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>67.34 ± 20.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer 0.2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>54.21 ± 5.79</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>64.65 ± 9.35</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>59.62 ± 10.91</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>59.97 ± 14.55</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>45.40 ± 16.47</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.13</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>45.38 ± 16.48</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>43.28 ± 10.57</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>21.36 ± 13.72</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>15.10 ± 11.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer 0.2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>66.08 ± 8.60</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>67.13 ± 7.79</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>67.37 ± 10.48</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>65.95 ± 24.03</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>54.82 ± 26.27</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.26 ± 0.18</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>59.78 ± 19.18</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>27.46 ± 12.81</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>28.56 ± 18.55</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>18.60 ± 15.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task 0.3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>54.72 ± 6.10</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>62.89 ± 7.17</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>61.04 ± 9.48</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>59.14 ± 12.04</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>42.27 ± 21.80</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.11</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>42.25 ± 21.81</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>42.81 ± 9.40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>19.72 ± 12.75</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>12.46 ± 11.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task 0.3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>84.52 ± 8.10</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>84.95 ± 9.79</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>85.60 ± 8.75</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>90.80 ± 7.46</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>80.91 ± 24.27</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.66 ± 0.22</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>80.88 ± 24.31</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>14.32 ± 7.77</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>71.95 ± 28.73</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>62.25 ± 30.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer 0.3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>55.14 ± 3.17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>64.80 ± 11.16</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>60.47 ± 14.25</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>60.11 ± 12.54</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>44.31 ± 21.73</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.10 ± 0.07</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>44.29 ± 21.73</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>42.92 ± 9.81</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>22.24 ± 11.43</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>13.59 ± 10.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer 0.3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>62.55 ± 12.88</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>67.97 ± 11.15</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>68.05 ± 10.41</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>69.75 ± 15.37</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>58.76 ± 25.87</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.27 ± 0.24</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>58.73 ± 25.89</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>34.91 ± 11.73</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>33.62 ± 26.76</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>27.22 ± 25.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task 0.4</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>55.71 ± 8.32</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>69.42 ± 7.88</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>65.56 ± 9.26</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>60.92 ± 11.25</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>42.00 ± 14.20</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.18</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>41.97 ± 14.20</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>42.85 ± 8.58</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>23.77 ± 16.21</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>17.03 ± 14.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task 0.4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>85.77 ± 8.65</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>88.10 ± 6.16</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>87.86 ± 6.54</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>90.48 ± 9.99</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>84.26 ± 10.12</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.71 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>84.23 ± 10.14</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15.61 ± 11.84</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>81.12 ± 16.33</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>74.07 ± 20.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer 0.4</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>52.07 ± 4.92</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>70.18 ± 4.83</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>63.83 ± 4.54</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>57.38 ± 9.31</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>37.95 ± 16.42</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>37.92 ± 16.42</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>45.07 ± 7.77</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>19.62 ± 15.03</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>12.32 ± 12.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer 0.4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>66.59 ± 8.90</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>72.89 ± 10.16</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>71.58 ± 11.02</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>76.39 ± 11.13</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>59.64 ± 18.53</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.33 ± 0.18</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>59.59 ± 18.56</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>28.72 ± 9.54</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>41.39 ± 26.26</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>28.89 ± 23.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task 0.5</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>55.25 ± 15.18</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>71.90 ± 13.47</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>67.71 ± 16.22</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>48.87 ± 19.25</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>29.02 ± 17.66</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.18</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>34.01 ± 15.71</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>42.45 ± 16.02</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>13.06 ± 15.85</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>9.04 ± 14.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task 0.5</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>80.76 ± 9.63</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>86.87 ± 6.12</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>86.56 ± 6.65</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>87.51 ± 11.07</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>75.75 ± 18.65</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.62 ± 0.18</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>75.70 ± 18.71</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>19.36 ± 11.80</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>72.32 ± 19.46</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>59.73 ± 27.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer 0.5</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>54.33 ± 15.16</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>74.30 ± 14.00</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>66.37 ± 17.28</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>47.30 ± 18.14</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>26.74 ± 13.65</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-0.01 ± 0.06</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>31.71 ± 12.01</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>43.63 ± 16.27</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>12.40 ± 9.57</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>6.40 ± 5.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer 0.5</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>57.81 ± 6.08</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>72.23 ± 7.60</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>69.77 ± 9.04</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>72.20 ± 9.54</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>46.10 ± 17.08</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.17 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>46.02 ± 17.13</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>33.94 ± 8.96</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>25.87 ± 15.37</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>17.89 ± 12.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task 0.6</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>54.81 ± 9.94</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>75.04 ± 10.04</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>72.07 ± 13.01</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>52.51 ± 25.63</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>31.41 ± 25.03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.17</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>36.39 ± 23.18</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>39.40 ± 19.20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>23.31 ± 22.87</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>17.00 ± 19.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task 0.6</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>82.65 ± 12.95</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>85.83 ± 7.95</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>85.99 ± 9.50</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>69.21 ± 36.45</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>62.44 ± 36.74</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.45 ± 0.30</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>72.41 ± 22.41</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>15.34 ± 14.44</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>70.88 ± 27.70</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>60.89 ± 35.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer 0.6</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>54.05 ± 12.65</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>76.31 ± 12.79</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>69.89 ± 17.87</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>56.07 ± 27.67</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>33.90 ± 23.69</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.08</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>38.87 ± 21.15</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>36.25 ± 19.79</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>28.04 ± 20.19</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>17.49 ± 14.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer 0.6</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>65.30 ± 16.16</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>74.87 ± 11.26</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>73.29 ± 15.42</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>55.58 ± 31.71</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>35.13 ± 29.85</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.14 ± 0.22</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>45.07 ± 24.29</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>26.97 ± 18.51</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>27.73 ± 32.52</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>18.20 ± 23.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task 0.7</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>62.13 ± 19.49</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>82.40 ± 9.97</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>79.47 ± 11.66</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>44.63 ± 25.71</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>21.57 ± 18.90</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.13</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>31.55 ± 18.05</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>37.17 ± 20.39</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>16.24 ± 14.41</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>9.99 ± 9.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task 0.7</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>87.86 ± 8.27</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>90.66 ± 6.05</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>91.61 ± 6.50</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>66.27 ± 43.78</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>64.16 ± 42.48</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.53 ± 0.37</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>79.16 ± 20.11</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8.41 ± 10.05</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>84.98 ± 13.93</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>81.91 ± 15.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer 0.7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>58.70 ± 20.78</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>80.49 ± 13.65</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>75.57 ± 17.26</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>46.22 ± 24.72</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>20.42 ± 16.03</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-0.03 ± 0.06</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>30.39 ± 15.77</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>34.77 ± 18.63</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>10.51 ± 12.35</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>6.83 ± 9.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer 0.7</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>69.69 ± 12.81</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>79.17 ± 8.02</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>78.63 ± 12.63</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>57.10 ± 38.30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>44.45 ± 31.35</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.22 ± 0.25</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>59.40 ± 13.23</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>17.15 ± 13.94</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>51.28 ± 24.21</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>38.30 ± 21.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task 0.8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>70.66 ± 19.52</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>81.71 ± 12.12</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>79.48 ± 16.71</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>38.20 ± 33.83</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>25.88 ± 27.90</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>45.87 ± 18.53</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>24.42 ± 22.89</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>28.33 ± 23.66</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>20.30 ± 21.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task 0.8</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>88.96 ± 10.98</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>91.41 ± 8.10</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>91.70 ± 8.83</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>64.23 ± 42.93</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>56.67 ± 39.87</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.48 ± 0.37</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>71.63 ± 20.39</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>9.84 ± 12.88</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>75.55 ± 31.25</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>72.48 ± 31.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer 0.8</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>68.01 ± 23.48</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>81.09 ± 15.09</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>76.31 ± 21.11</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>38.22 ± 36.90</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>29.16 ± 31.45</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-0.01 ± 0.05</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>49.15 ± 20.56</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>22.63 ± 23.99</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>29.07 ± 28.54</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>21.43 ± 26.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer 0.8</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>72.22 ± 21.65</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>81.05 ± 14.93</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>80.59 ± 16.15</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>51.82 ± 36.73</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>35.15 ± 33.17</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.15 ± 0.28</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>50.09 ± 23.91</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20.86 ± 19.15</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>35.93 ± 35.54</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>26.93 ± 30.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task 0.9</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>64.46 ± 18.15</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>83.97 ± 6.48</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>82.10 ± 10.08</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>45.53 ± 32.12</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>22.06 ± 21.06</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.11</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>37.05 ± 17.51</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>26.24 ± 19.69</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>20.95 ± 19.25</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>11.64 ± 12.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task 0.9</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>85.16 ± 17.40</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>91.39 ± 8.92</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>91.04 ± 10.17</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>62.26 ± 42.94</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>52.95 ± 42.56</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.46 ± 0.40</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>67.93 ± 27.37</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10.61 ± 15.15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>68.37 ± 39.93</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>64.33 ± 38.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr AvP Task, No Accelerometer 0.9</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>61.52 ± 18.15</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>83.13 ± 6.68</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>80.15 ± 10.90</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>47.26 ± 33.18</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>21.89 ± 21.42</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.05</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>36.87 ± 18.10</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>25.42 ± 19.05</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>18.14 ± 17.86</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>11.22 ± 16.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>cLACIr Int Task, No Accelerometer 0.9</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>68.18 ± 19.43</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>83.09 ± 11.22</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>82.07 ± 12.75</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>51.02 ± 37.68</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>33.25 ± 27.64</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.11 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>48.19 ± 17.09</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>22.92 ± 20.80</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>36.39 ± 24.97</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>26.00 ± 22.88</t>
         </is>
       </c>
     </row>
